--- a/inputdata/inputdata_hybridDC.xlsx
+++ b/inputdata/inputdata_hybridDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E332BD05-FEDE-4D12-BC3B-E2C26669BF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB11ED56-0F04-4CE1-AB06-4131F50409D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1212,13 +1212,13 @@
     <t>Use_Database_PV</t>
   </si>
   <si>
-    <t>N_modules</t>
-  </si>
-  <si>
     <t>Set to 2 to use CEC database (1 = Manual Mode, 2 = Use Database)</t>
   </si>
   <si>
     <t>Set to 2 to use PVlite database (1 = Manual Mode, 2 = Use Database)</t>
+  </si>
+  <si>
+    <t>N_Modules</t>
   </si>
 </sst>
 </file>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
@@ -9827,7 +9827,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C6" s="110">
         <v>4</v>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">

--- a/inputdata/inputdata_hybridDC.xlsx
+++ b/inputdata/inputdata_hybridDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB11ED56-0F04-4CE1-AB06-4131F50409D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F88F7E-E8E5-44E4-ACE2-A88D0681C9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="6" r:id="rId1"/>
@@ -9098,7 +9098,9 @@
       <c r="B11" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="C11" s="20"/>
+      <c r="C11" s="20">
+        <v>0</v>
+      </c>
       <c r="D11" s="23" t="s">
         <v>7</v>
       </c>

--- a/inputdata/inputdata_hybridDC.xlsx
+++ b/inputdata/inputdata_hybridDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F88F7E-E8E5-44E4-ACE2-A88D0681C9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19BE9B5-8C2C-453F-8F9D-337D6F44B45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="6" r:id="rId1"/>
@@ -9801,7 +9801,7 @@
         <v>303</v>
       </c>
       <c r="C4" s="110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
@@ -10186,7 +10186,7 @@
         <v>301</v>
       </c>
       <c r="C4" s="110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
@@ -10815,7 +10815,7 @@
         <v>294</v>
       </c>
       <c r="C4" s="110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
